--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,98 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/tmk/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_00F124D0156748DFE54878D6425DCE3A874750C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BB0AAB4-F852-4B46-A3E4-659BDC8C2D56}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Año</t>
-  </si>
-  <si>
-    <t>Mes</t>
-  </si>
-  <si>
-    <t>Concepto</t>
-  </si>
-  <si>
-    <t>Rol</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Meta</t>
-  </si>
-  <si>
-    <t>Ejecutado</t>
-  </si>
-  <si>
-    <t>% Cumplimiento</t>
-  </si>
-  <si>
-    <t>Pago cumplimiento</t>
-  </si>
-  <si>
-    <t>Usuario cambio</t>
-  </si>
-  <si>
-    <t>Fecha cambio</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -107,44 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -432,152 +424,560 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rol</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ejecutado</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>% Cumplimiento</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Pago cumplimiento</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Usuario cambio</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha cambio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Venta directa - salarial</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Natalia  Giraldo Galeano</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>110.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Venta directa - salarial</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Raiza Lorena Urzola Lora</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Venta directa - salarial</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yessica Yulieth Moreno</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Referido - bono</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Natalia  Giraldo Galeano</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>160.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Referido - bono</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Raiza Lorena Urzola Lora</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" t="n">
+        <v>67</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>167.5%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Referido - bono</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Yessica Yulieth Moreno</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>120.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Venta directa - salarial</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Líder</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Maria Deisy Gil Gomez</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>44.2%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Referido - bono</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Líder</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Maria Deisy Gil Gomez</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>179</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>89.5%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pyme Móvil - salarial</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Líder</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Maria Deisy Gil Gomez</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K37" s="2"/>
+      <c r="G10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sin meta</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLOUND - salarial</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Líder</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Maria Deisy Gil Gomez</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sin meta</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>46070.45920405041</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/02 Febrero/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DDC35D9-D645-40B6-B7D9-E184D1DA433F}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF902C1F-1ADE-4112-9F0C-E5EC5986F2E3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="44">
   <si>
     <t>Año</t>
   </si>
@@ -125,6 +125,33 @@
   </si>
   <si>
     <t>90%</t>
+  </si>
+  <si>
+    <t>Febrero</t>
+  </si>
+  <si>
+    <t>113.3%</t>
+  </si>
+  <si>
+    <t>80.7%</t>
+  </si>
+  <si>
+    <t>104.0%</t>
+  </si>
+  <si>
+    <t>52.0%</t>
+  </si>
+  <si>
+    <t>116.0%</t>
+  </si>
+  <si>
+    <t>68.0%</t>
+  </si>
+  <si>
+    <t>122.0%</t>
+  </si>
+  <si>
+    <t>96.0%</t>
   </si>
 </sst>
 </file>
@@ -132,7 +159,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -188,7 +215,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,9 +518,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -564,7 +594,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -599,7 +629,7 @@
         <v>17</v>
       </c>
       <c r="K3" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -634,7 +664,7 @@
         <v>17</v>
       </c>
       <c r="K4" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -669,7 +699,7 @@
         <v>17</v>
       </c>
       <c r="K5" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -704,7 +734,7 @@
         <v>17</v>
       </c>
       <c r="K6" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -739,7 +769,7 @@
         <v>17</v>
       </c>
       <c r="K7" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -774,7 +804,7 @@
         <v>17</v>
       </c>
       <c r="K8" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -809,7 +839,7 @@
         <v>17</v>
       </c>
       <c r="K9" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -844,7 +874,7 @@
         <v>17</v>
       </c>
       <c r="K10" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -879,7 +909,357 @@
         <v>17</v>
       </c>
       <c r="K11" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12">
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>61</v>
+      </c>
+      <c r="H13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2026</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14">
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2026</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>58</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2026</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16">
+        <v>25</v>
+      </c>
+      <c r="G16">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2026</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>50</v>
+      </c>
+      <c r="G17">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18">
+        <v>75</v>
+      </c>
+      <c r="G18">
+        <v>60.5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2026</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19">
+        <v>150</v>
+      </c>
+      <c r="G19">
+        <v>170</v>
+      </c>
+      <c r="H19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2026</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21">
+        <v>100000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="2">
+        <v>46099.788829440811</v>
       </c>
     </row>
   </sheetData>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/02 Febrero/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/03 Marzo/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF902C1F-1ADE-4112-9F0C-E5EC5986F2E3}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4306C51-4C35-4DE7-8B71-69E85897D3C8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="53">
   <si>
     <t>Año</t>
   </si>
@@ -152,6 +152,33 @@
   </si>
   <si>
     <t>96.0%</t>
+  </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
+    <t>61.3%</t>
+  </si>
+  <si>
+    <t>112.7%</t>
+  </si>
+  <si>
+    <t>125.0%</t>
+  </si>
+  <si>
+    <t>137.5%</t>
+  </si>
+  <si>
+    <t>94.7%</t>
+  </si>
+  <si>
+    <t>150.0%</t>
+  </si>
+  <si>
+    <t>56.0%</t>
+  </si>
+  <si>
+    <t>158.0%</t>
   </si>
 </sst>
 </file>
@@ -518,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -1262,6 +1289,356 @@
         <v>46099.788829440811</v>
       </c>
     </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2026</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22">
+        <v>75</v>
+      </c>
+      <c r="G22">
+        <v>46</v>
+      </c>
+      <c r="H22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2026</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23">
+        <v>150</v>
+      </c>
+      <c r="G23">
+        <v>169</v>
+      </c>
+      <c r="H23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2026</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24">
+        <v>60</v>
+      </c>
+      <c r="G24">
+        <v>11</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2026</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25">
+        <v>100000</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2026</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>33</v>
+      </c>
+      <c r="H27" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2026</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28">
+        <v>19</v>
+      </c>
+      <c r="G28">
+        <v>18</v>
+      </c>
+      <c r="H28" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2026</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29">
+        <v>38</v>
+      </c>
+      <c r="G29">
+        <v>57</v>
+      </c>
+      <c r="H29" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2026</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30">
+        <v>25</v>
+      </c>
+      <c r="G30">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2026</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31">
+        <v>50</v>
+      </c>
+      <c r="G31">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/03 Marzo/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/05 Mayo/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4306C51-4C35-4DE7-8B71-69E85897D3C8}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E453AE74-D06B-4AEB-A206-9D4E1BE3A795}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="62">
   <si>
     <t>Año</t>
   </si>
@@ -179,6 +179,33 @@
   </si>
   <si>
     <t>158.0%</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>70.0%</t>
+  </si>
+  <si>
+    <t>108.7%</t>
+  </si>
+  <si>
+    <t>64.0%</t>
+  </si>
+  <si>
+    <t>102.0%</t>
+  </si>
+  <si>
+    <t>88.0%</t>
+  </si>
+  <si>
+    <t>114.0%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>100.0%</t>
   </si>
 </sst>
 </file>
@@ -545,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -1639,6 +1666,356 @@
         <v>46135.554853843933</v>
       </c>
     </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2026</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32">
+        <v>75</v>
+      </c>
+      <c r="G32">
+        <v>52.5</v>
+      </c>
+      <c r="H32" t="s">
+        <v>54</v>
+      </c>
+      <c r="I32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2026</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33">
+        <v>150</v>
+      </c>
+      <c r="G33">
+        <v>163</v>
+      </c>
+      <c r="H33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2026</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34">
+        <v>60</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>29</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2026</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35">
+        <v>100000</v>
+      </c>
+      <c r="G35">
+        <v>2153085</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>29</v>
+      </c>
+      <c r="J35" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2026</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36">
+        <v>25</v>
+      </c>
+      <c r="G36">
+        <v>16</v>
+      </c>
+      <c r="H36" t="s">
+        <v>56</v>
+      </c>
+      <c r="I36" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2026</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37">
+        <v>50</v>
+      </c>
+      <c r="G37">
+        <v>51</v>
+      </c>
+      <c r="H37" t="s">
+        <v>57</v>
+      </c>
+      <c r="I37" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2026</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38">
+        <v>25</v>
+      </c>
+      <c r="G38">
+        <v>22</v>
+      </c>
+      <c r="H38" t="s">
+        <v>58</v>
+      </c>
+      <c r="I38" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2026</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39">
+        <v>50</v>
+      </c>
+      <c r="G39">
+        <v>57</v>
+      </c>
+      <c r="H39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2026</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40">
+        <v>25</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
+      </c>
+      <c r="H40" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2026</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41">
+        <v>50</v>
+      </c>
+      <c r="G41">
+        <v>50</v>
+      </c>
+      <c r="H41" t="s">
+        <v>61</v>
+      </c>
+      <c r="I41" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="2">
+        <v>46195.587666611427</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/05 Mayo/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E453AE74-D06B-4AEB-A206-9D4E1BE3A795}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB224E1A-501A-424E-A532-9CC6366AB4BB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="68">
   <si>
     <t>Año</t>
   </si>
@@ -206,6 +206,24 @@
   </si>
   <si>
     <t>100.0%</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>100.7%</t>
+  </si>
+  <si>
+    <t>72.0%</t>
+  </si>
+  <si>
+    <t>76.0%</t>
+  </si>
+  <si>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>130.0%</t>
   </si>
 </sst>
 </file>
@@ -572,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -2016,6 +2034,356 @@
         <v>46195.587666611427</v>
       </c>
     </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2026</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42">
+        <v>75</v>
+      </c>
+      <c r="G42">
+        <v>75.5</v>
+      </c>
+      <c r="H42" t="s">
+        <v>63</v>
+      </c>
+      <c r="I42" t="s">
+        <v>29</v>
+      </c>
+      <c r="J42" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2026</v>
+      </c>
+      <c r="B43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43">
+        <v>150</v>
+      </c>
+      <c r="G43">
+        <v>174</v>
+      </c>
+      <c r="H43" t="s">
+        <v>40</v>
+      </c>
+      <c r="I43" t="s">
+        <v>29</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2026</v>
+      </c>
+      <c r="B44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44">
+        <v>60</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2026</v>
+      </c>
+      <c r="B45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45">
+        <v>100000</v>
+      </c>
+      <c r="G45">
+        <v>259090</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46">
+        <v>25</v>
+      </c>
+      <c r="G46">
+        <v>18</v>
+      </c>
+      <c r="H46" t="s">
+        <v>64</v>
+      </c>
+      <c r="I46" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="G47">
+        <v>52</v>
+      </c>
+      <c r="H47" t="s">
+        <v>38</v>
+      </c>
+      <c r="I47" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48">
+        <v>25</v>
+      </c>
+      <c r="G48">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2026</v>
+      </c>
+      <c r="B49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49">
+        <v>50</v>
+      </c>
+      <c r="G49">
+        <v>57</v>
+      </c>
+      <c r="H49" t="s">
+        <v>59</v>
+      </c>
+      <c r="I49" t="s">
+        <v>29</v>
+      </c>
+      <c r="J49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2026</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50">
+        <v>25</v>
+      </c>
+      <c r="G50">
+        <v>20</v>
+      </c>
+      <c r="H50" t="s">
+        <v>66</v>
+      </c>
+      <c r="I50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2026</v>
+      </c>
+      <c r="B51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51">
+        <v>50</v>
+      </c>
+      <c r="G51">
+        <v>65</v>
+      </c>
+      <c r="H51" t="s">
+        <v>67</v>
+      </c>
+      <c r="I51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="2">
+        <v>46195.596720197493</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/05 Mayo/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/06 Junio/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB224E1A-501A-424E-A532-9CC6366AB4BB}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{929A1B8D-24D4-4F8F-A26F-FB55C8D1374A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="74">
   <si>
     <t>Año</t>
   </si>
@@ -224,6 +224,24 @@
   </si>
   <si>
     <t>130.0%</t>
+  </si>
+  <si>
+    <t>Junio</t>
+  </si>
+  <si>
+    <t>106.0%</t>
+  </si>
+  <si>
+    <t>112.0%</t>
+  </si>
+  <si>
+    <t>166.0%</t>
+  </si>
+  <si>
+    <t>48.0%</t>
+  </si>
+  <si>
+    <t>78.0%</t>
   </si>
 </sst>
 </file>
@@ -590,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -2066,7 +2084,7 @@
         <v>17</v>
       </c>
       <c r="K42" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2101,7 +2119,7 @@
         <v>17</v>
       </c>
       <c r="K43" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2136,7 +2154,7 @@
         <v>17</v>
       </c>
       <c r="K44" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2171,7 +2189,7 @@
         <v>17</v>
       </c>
       <c r="K45" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2206,7 +2224,7 @@
         <v>17</v>
       </c>
       <c r="K46" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2241,7 +2259,7 @@
         <v>17</v>
       </c>
       <c r="K47" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2276,7 +2294,7 @@
         <v>17</v>
       </c>
       <c r="K48" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2311,7 +2329,7 @@
         <v>17</v>
       </c>
       <c r="K49" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2346,7 +2364,7 @@
         <v>17</v>
       </c>
       <c r="K50" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2381,7 +2399,777 @@
         <v>17</v>
       </c>
       <c r="K51" s="2">
-        <v>46195.596720197493</v>
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2026</v>
+      </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52">
+        <v>25</v>
+      </c>
+      <c r="G52">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>66</v>
+      </c>
+      <c r="I52" t="s">
+        <v>29</v>
+      </c>
+      <c r="J52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="2">
+        <v>46226.635234062502</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2026</v>
+      </c>
+      <c r="B53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>52</v>
+      </c>
+      <c r="H53" t="s">
+        <v>38</v>
+      </c>
+      <c r="I53" t="s">
+        <v>29</v>
+      </c>
+      <c r="J53" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53" s="2">
+        <v>46226.635234062502</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2026</v>
+      </c>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54">
+        <v>75</v>
+      </c>
+      <c r="G54">
+        <v>75.5</v>
+      </c>
+      <c r="H54" t="s">
+        <v>63</v>
+      </c>
+      <c r="I54" t="s">
+        <v>29</v>
+      </c>
+      <c r="J54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2026</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55">
+        <v>150</v>
+      </c>
+      <c r="G55">
+        <v>159</v>
+      </c>
+      <c r="H55" t="s">
+        <v>69</v>
+      </c>
+      <c r="I55" t="s">
+        <v>29</v>
+      </c>
+      <c r="J55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2026</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56">
+        <v>60</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2026</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57">
+        <v>100000</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2026</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58">
+        <v>25</v>
+      </c>
+      <c r="G58">
+        <v>28</v>
+      </c>
+      <c r="H58" t="s">
+        <v>70</v>
+      </c>
+      <c r="I58" t="s">
+        <v>29</v>
+      </c>
+      <c r="J58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2026</v>
+      </c>
+      <c r="B59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59">
+        <v>50</v>
+      </c>
+      <c r="G59">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s">
+        <v>71</v>
+      </c>
+      <c r="I59" t="s">
+        <v>29</v>
+      </c>
+      <c r="J59" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2026</v>
+      </c>
+      <c r="B60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60">
+        <v>25</v>
+      </c>
+      <c r="G60">
+        <v>12</v>
+      </c>
+      <c r="H60" t="s">
+        <v>72</v>
+      </c>
+      <c r="I60" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2026</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61">
+        <v>50</v>
+      </c>
+      <c r="G61">
+        <v>38</v>
+      </c>
+      <c r="H61" t="s">
+        <v>65</v>
+      </c>
+      <c r="I61" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" t="s">
+        <v>17</v>
+      </c>
+      <c r="K61" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2026</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62">
+        <v>25</v>
+      </c>
+      <c r="G62">
+        <v>17</v>
+      </c>
+      <c r="H62" t="s">
+        <v>41</v>
+      </c>
+      <c r="I62" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2026</v>
+      </c>
+      <c r="B63" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <v>50</v>
+      </c>
+      <c r="G63">
+        <v>39</v>
+      </c>
+      <c r="H63" t="s">
+        <v>73</v>
+      </c>
+      <c r="I63" t="s">
+        <v>16</v>
+      </c>
+      <c r="J63" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2026</v>
+      </c>
+      <c r="B64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64">
+        <v>75</v>
+      </c>
+      <c r="G64">
+        <v>75.5</v>
+      </c>
+      <c r="H64" t="s">
+        <v>63</v>
+      </c>
+      <c r="I64" t="s">
+        <v>29</v>
+      </c>
+      <c r="J64" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2026</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" t="s">
+        <v>24</v>
+      </c>
+      <c r="F65">
+        <v>150</v>
+      </c>
+      <c r="G65">
+        <v>159</v>
+      </c>
+      <c r="H65" t="s">
+        <v>69</v>
+      </c>
+      <c r="I65" t="s">
+        <v>29</v>
+      </c>
+      <c r="J65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2026</v>
+      </c>
+      <c r="B66" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66">
+        <v>60</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2026</v>
+      </c>
+      <c r="B67" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67">
+        <v>100000</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>16</v>
+      </c>
+      <c r="I67" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2026</v>
+      </c>
+      <c r="B68" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68">
+        <v>25</v>
+      </c>
+      <c r="G68">
+        <v>28</v>
+      </c>
+      <c r="H68" t="s">
+        <v>70</v>
+      </c>
+      <c r="I68" t="s">
+        <v>29</v>
+      </c>
+      <c r="J68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2026</v>
+      </c>
+      <c r="B69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69">
+        <v>50</v>
+      </c>
+      <c r="G69">
+        <v>83</v>
+      </c>
+      <c r="H69" t="s">
+        <v>71</v>
+      </c>
+      <c r="I69" t="s">
+        <v>29</v>
+      </c>
+      <c r="J69" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2026</v>
+      </c>
+      <c r="B70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70">
+        <v>25</v>
+      </c>
+      <c r="G70">
+        <v>12</v>
+      </c>
+      <c r="H70" t="s">
+        <v>72</v>
+      </c>
+      <c r="I70" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2026</v>
+      </c>
+      <c r="B71" t="s">
+        <v>68</v>
+      </c>
+      <c r="C71" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71">
+        <v>50</v>
+      </c>
+      <c r="G71">
+        <v>38</v>
+      </c>
+      <c r="H71" t="s">
+        <v>65</v>
+      </c>
+      <c r="I71" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" t="s">
+        <v>17</v>
+      </c>
+      <c r="K71" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2026</v>
+      </c>
+      <c r="B72" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72">
+        <v>25</v>
+      </c>
+      <c r="G72">
+        <v>17</v>
+      </c>
+      <c r="H72" t="s">
+        <v>41</v>
+      </c>
+      <c r="I72" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" s="2">
+        <v>46226.753580955083</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2026</v>
+      </c>
+      <c r="B73" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73">
+        <v>50</v>
+      </c>
+      <c r="G73">
+        <v>39</v>
+      </c>
+      <c r="H73" t="s">
+        <v>73</v>
+      </c>
+      <c r="I73" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" s="2">
+        <v>46226.753580955083</v>
       </c>
     </row>
   </sheetData>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/06 Junio/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{929A1B8D-24D4-4F8F-A26F-FB55C8D1374A}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DFDD8B8-67E4-4572-8F38-46F75741B918}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="74">
   <si>
     <t>Año</t>
   </si>
@@ -251,7 +264,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,6 +276,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -297,18 +317,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2947,13 +2970,14 @@
         <v>100000</v>
       </c>
       <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67" t="s">
-        <v>16</v>
+        <v>107085</v>
+      </c>
+      <c r="H67" s="3">
+        <f>G67/F67</f>
+        <v>1.0708500000000001</v>
       </c>
       <c r="I67" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J67" t="s">
         <v>17</v>
